--- a/r4-ELGA-AustrianPatientSummary-fix-pipeline/StructureDefinition-at-aps-medication.xlsx
+++ b/r4-ELGA-AustrianPatientSummary-fix-pipeline/StructureDefinition-at-aps-medication.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-02-16T12:34:18+00:00</t>
+    <t>2026-02-16T16:11:34+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
